--- a/tool/cmd/gen-go-db/gendb/mps-template.xlsx
+++ b/tool/cmd/gen-go-db/gendb/mps-template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="125">
   <si>
     <t>列名</t>
   </si>
@@ -375,6 +375,9 @@
     <t>1-男 2-女</t>
   </si>
   <si>
+    <t>///@omitempty</t>
+  </si>
+  <si>
     <t>TM_TEST_UNIUQE_1</t>
   </si>
   <si>
@@ -385,6 +388,21 @@
   </si>
   <si>
     <t>PHONE = @Phone</t>
+  </si>
+  <si>
+    <t>FindAllColsByPage</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>ADDRESS = @Address</t>
+  </si>
+  <si>
+    <t>FindAaByPage</t>
+  </si>
+  <si>
+    <t>FindAllCols</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1086,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1101,9 +1119,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2406,25 +2421,25 @@
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:9">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="12" t="s">
+      <c r="C51" s="11"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12" t="s">
+      <c r="G51" s="11"/>
+      <c r="H51" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I51" s="13"/>
+      <c r="I51" s="12"/>
     </row>
     <row r="52" customFormat="1"/>
     <row r="53" customFormat="1"/>
@@ -2438,7 +2453,7 @@
     <row r="61" customFormat="1"/>
     <row r="62" customFormat="1"/>
     <row r="63" customFormat="1" spans="1:9">
-      <c r="B63" s="15"/>
+      <c r="B63" s="14"/>
     </row>
     <row r="64" customFormat="1"/>
     <row r="65" customFormat="1"/>
@@ -2452,7 +2467,7 @@
       </c>
     </row>
     <row r="80" spans="5:5">
-      <c r="E80" s="16" t="s">
+      <c r="E80" s="15" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2566,7 +2581,9 @@
       <c r="G3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="3" t="s">
@@ -2705,7 +2722,7 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>53</v>
@@ -2719,7 +2736,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:9">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>41</v>
@@ -2760,32 +2777,82 @@
       <c r="H21" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:9">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12" t="s">
+      <c r="B22" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12" t="s">
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:9">
+      <c r="A23" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" customFormat="1"/>
-    <row r="24" customFormat="1"/>
-    <row r="25" customFormat="1"/>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:9">
+      <c r="A24" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="13"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:9">
+      <c r="A25" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+    </row>
     <row r="26" customFormat="1"/>
     <row r="27" customFormat="1"/>
     <row r="28" customFormat="1"/>
@@ -2795,7 +2862,7 @@
     <row r="32" customFormat="1"/>
     <row r="33" customFormat="1"/>
     <row r="34" customFormat="1" spans="2:2">
-      <c r="B34" s="15"/>
+      <c r="B34" s="14"/>
     </row>
     <row r="35" customFormat="1"/>
     <row r="36" customFormat="1"/>
@@ -2809,7 +2876,7 @@
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="5:5">
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="15" t="s">
         <v>107</v>
       </c>
     </row>

--- a/tool/cmd/gen-go-db/gendb/mps-template.xlsx
+++ b/tool/cmd/gen-go-db/gendb/mps-template.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="TM_MEDIA_ACT" sheetId="1" r:id="rId1"/>
-    <sheet name="TM_TEST" sheetId="2" r:id="rId2"/>
+    <sheet name="tbl_3ds_request" sheetId="3" r:id="rId2"/>
+    <sheet name="TM_TEST" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="233">
   <si>
     <t>列名</t>
   </si>
@@ -369,6 +370,333 @@
     <t>not in</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>数据表自增长ID(@readonly@)</t>
+  </si>
+  <si>
+    <t>CLUSTER_ID</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>在线库集群ID(第一位：集群ID（使用1-9）；第二位：表ID（取值A/B）。@readonly@)</t>
+  </si>
+  <si>
+    <t>TRANSACTION_TYPE</t>
+  </si>
+  <si>
+    <t>交易类型(01-DCC预支付,02-消费,03-消费撤销,04-消费冲正，05-消费撤销冲正（暂不支持），06-预授权，07-预授权撤销，08-预授权冲正，09-预授权撤销冲正（暂不支持），10-预授权完成，11-预授权完成撤销，12-预授权完成冲正，13-预授权完成撤销冲正（暂不支持），14-账户验证，20-退货；50-交易状态查询，61-3DS认证初始化,62-3DS认证，63-3DS认证挑战；81-拒付，82-再请款，83-收费，84-付费,85-拒付撤销，86-再请款撤销，87-收单行收费，88-收单行付费；90-回响测试，91-签到，92-签退，93-密钥切换，94-RECON，95-风险报告，96-文本通知（或有）。@enumType=com.allinfinance.marcopolo.enums.TransactionType@)</t>
+  </si>
+  <si>
+    <t>ORDER_ID</t>
+  </si>
+  <si>
+    <t>商户交易订单号</t>
+  </si>
+  <si>
+    <t>GATEWAY_SERVICE_KEY</t>
+  </si>
+  <si>
+    <t>网关微服务ID，全局跟踪号的第一部分(IP:Port#微服务ID)</t>
+  </si>
+  <si>
+    <t>GLOBAL_TRACE_NO</t>
+  </si>
+  <si>
+    <t>全局跟踪号第二部分，也用于同步转异步Key(与网关ID配合使用，YYYYMMDDHHMMSSmmm+10序列号)</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>FLD2(存储加密)</t>
+  </si>
+  <si>
+    <t>PROCESSING_CODE</t>
+  </si>
+  <si>
+    <t>FLD3</t>
+  </si>
+  <si>
+    <t>ORDER_AMOUNT</t>
+  </si>
+  <si>
+    <t>订单金额</t>
+  </si>
+  <si>
+    <t>TRANSACTION_AMOUNT</t>
+  </si>
+  <si>
+    <t>FLD4(精确到分)</t>
+  </si>
+  <si>
+    <t>BILLING_AMOUNT</t>
+  </si>
+  <si>
+    <t>FLD6(精确到分，DCC由收单行提供该金额)</t>
+  </si>
+  <si>
+    <t>TRANSMISSION_DATETIME</t>
+  </si>
+  <si>
+    <t>FLD7</t>
+  </si>
+  <si>
+    <t>CONVERSION_RATE_BILLING</t>
+  </si>
+  <si>
+    <t>FLD10(卡组织汇率表示方式，参考卡组织规范。DCC情况下该汇率由银行提供（为包括了上浮部分的实际汇率）)</t>
+  </si>
+  <si>
+    <t>STAN</t>
+  </si>
+  <si>
+    <t>FLD11</t>
+  </si>
+  <si>
+    <t>LOCAL_TIME</t>
+  </si>
+  <si>
+    <t>FLD12</t>
+  </si>
+  <si>
+    <t>LOCAL_DATE</t>
+  </si>
+  <si>
+    <t>FLD13</t>
+  </si>
+  <si>
+    <t>MCC</t>
+  </si>
+  <si>
+    <t>FLD18</t>
+  </si>
+  <si>
+    <t>ACQUIRING_INST_COUNTRY_CODE</t>
+  </si>
+  <si>
+    <t>FLD19</t>
+  </si>
+  <si>
+    <t>POS_ENTRY_MODE</t>
+  </si>
+  <si>
+    <t>FLD22</t>
+  </si>
+  <si>
+    <t>POS_CONDITION_CODE</t>
+  </si>
+  <si>
+    <t>FLD25</t>
+  </si>
+  <si>
+    <t>POS_PIN_CAPTURE_CODE</t>
+  </si>
+  <si>
+    <t>FLD26</t>
+  </si>
+  <si>
+    <t>ACQUIRING_INSTITUTION</t>
+  </si>
+  <si>
+    <t>FLD32</t>
+  </si>
+  <si>
+    <t>RETRIEVAL_REFERENCE_NUMBER</t>
+  </si>
+  <si>
+    <t>FLD37(最后一位是集群单元ID号)</t>
+  </si>
+  <si>
+    <t>TERMINAL_ID</t>
+  </si>
+  <si>
+    <t>FLD41</t>
+  </si>
+  <si>
+    <t>MERCHANT_ID</t>
+  </si>
+  <si>
+    <t>FLD42，厦门国际构成：2位机构号+3位分行号+4位MCC+后2位机构号4位商户序号或6位商户序号；其他行构成：4位分行号+4位MCC+4位机构号（首位不为9）|3位顺序号或9|6位顺序号</t>
+  </si>
+  <si>
+    <t>CARD_ACCEPTOR_LOCATION</t>
+  </si>
+  <si>
+    <t>FLD43</t>
+  </si>
+  <si>
+    <t>ORDER_CURRENCY</t>
+  </si>
+  <si>
+    <t>订单币种(联机参数)</t>
+  </si>
+  <si>
+    <t>TRANSACTION_CURRENCY</t>
+  </si>
+  <si>
+    <t>FLD49(考虑境外外卡收单场景，该字段可能不为156)</t>
+  </si>
+  <si>
+    <t>BILLING_CURRENCY</t>
+  </si>
+  <si>
+    <t>FLD51</t>
+  </si>
+  <si>
+    <t>ADDITIONAL_POS_DATA</t>
+  </si>
+  <si>
+    <t>FLD60/DE61(VISA长度12，MC长度26)</t>
+  </si>
+  <si>
+    <t>CARD_TYPE</t>
+  </si>
+  <si>
+    <t>卡片类型(V-VISA；M-MC；J-JCB；A-AMEX；D-DC；C-CUP。@enumType=com.allinfinance.marcopolo.enums.CardType@)</t>
+  </si>
+  <si>
+    <t>DCC_FLAG</t>
+  </si>
+  <si>
+    <t>DCC标记(1-DCC交易；0-非DCC交易。@enumType=com.allinfinance.marcopolo.enums.DccFlag@)</t>
+  </si>
+  <si>
+    <t>KEY_DATETIME</t>
+  </si>
+  <si>
+    <t>加密存储数据时的密钥版本(YYYYMMDDHHMMSS)</t>
+  </si>
+  <si>
+    <t>DEVICE_TYPE</t>
+  </si>
+  <si>
+    <t>设备备注字段(取值: WEB/ANDROID/IOS/CONSOLE等。@enumType=com.allinfinance.marcopolo.enums.DeviceType@)</t>
+  </si>
+  <si>
+    <t>INTERFACE_VERSION</t>
+  </si>
+  <si>
+    <t>商户接口版本(取值：O1.0/O1.1/P1.0等 O代表线上，P代表线下)</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>终端或持卡人浏览器IP地址(支持IP4和IP6，备注字段)</t>
+  </si>
+  <si>
+    <t>RISK_SERVICE_FLAG</t>
+  </si>
+  <si>
+    <t>商户上送的风险评估服务标记(0-不使用，1-使用。老系统必须取值1。@enumType=com.allinfinance.marcopolo.enums.RiskServiceFlag@)</t>
+  </si>
+  <si>
+    <t>PAYMENT_TYPE</t>
+  </si>
+  <si>
+    <t>支付类型(0-线下，1-Normal E-Commerce,2-3DS ,4- 控台手工发起。@enumType=com.allinfinance.marcopolo.enums.PaymentType@)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_COUNTRY</t>
+  </si>
+  <si>
+    <t>持卡人国籍(2位国家字母简写)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_ADDRESS</t>
+  </si>
+  <si>
+    <t>持卡人地址</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_NAME</t>
+  </si>
+  <si>
+    <t>持卡人名称(加密存放)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_STATE</t>
+  </si>
+  <si>
+    <t>持卡人州省(需要符合ISO3166-2中State-code)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_CITY</t>
+  </si>
+  <si>
+    <t>持卡人城市</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_ZIP_CODE</t>
+  </si>
+  <si>
+    <t>持卡人邮编</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_PHONE</t>
+  </si>
+  <si>
+    <t>持卡人电话(加密存放)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_EMAIL</t>
+  </si>
+  <si>
+    <t>持卡人EMAIL(加密存放)</t>
+  </si>
+  <si>
+    <t>RESERVED_1</t>
+  </si>
+  <si>
+    <t>保留字段1</t>
+  </si>
+  <si>
+    <t>RESERVED_2</t>
+  </si>
+  <si>
+    <t>保留字段2</t>
+  </si>
+  <si>
+    <t>INSERT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP(6)</t>
+  </si>
+  <si>
+    <t>记录创建时间戳</t>
+  </si>
+  <si>
+    <t>INSERT_USER</t>
+  </si>
+  <si>
+    <t>记录创建人(用户名或程序名)</t>
+  </si>
+  <si>
+    <t>IDX_RRN</t>
+  </si>
+  <si>
+    <t>IDX_INSERT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>IDX_ORDER_ID</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>RETRIEVAL_REFERENCE_NUMBER = @RRN</t>
+  </si>
+  <si>
     <t>SEX</t>
   </si>
   <si>
@@ -391,9 +719,6 @@
   </si>
   <si>
     <t>FindAllColsByPage</t>
-  </si>
-  <si>
-    <t>*</t>
   </si>
   <si>
     <t>ADDRESS = @Address</t>
@@ -1086,7 +1411,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1126,11 +1451,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1218,7 +1552,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4020820" y="401955"/>
+          <a:off x="4023995" y="401955"/>
           <a:ext cx="1027430" cy="1050290"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
@@ -1261,6 +1595,7 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
@@ -1622,14 +1957,14 @@
   <dimension ref="A1:I85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="67.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="67.6666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="54.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="54.3333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6666666666667" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2467,7 +2802,7 @@
       </c>
     </row>
     <row r="80" spans="5:5">
-      <c r="E80" s="15" t="s">
+      <c r="E80" s="18" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2507,21 +2842,1267 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="30.8333333333333" style="12" customWidth="1"/>
+    <col min="2" max="2" width="29.8333333333333" style="12" customWidth="1"/>
+    <col min="3" max="3" width="13" style="12" customWidth="1"/>
+    <col min="4" max="4" width="18.6666666666667" style="12" customWidth="1"/>
+    <col min="5" max="5" width="113.5" style="12" customWidth="1"/>
+    <col min="6" max="6" width="18.6666666666667" style="12" customWidth="1"/>
+    <col min="7" max="7" width="255.833333333333" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="10.8333333333333" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="12">
+        <v>2</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12">
+        <v>24</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="12">
+        <v>64</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="12">
+        <v>32</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="12">
+        <v>64</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="12">
+        <v>6</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="12">
+        <v>10</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="12">
+        <v>8</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="12">
+        <v>6</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="12">
+        <v>6</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="12">
+        <v>4</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="12">
+        <v>4</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="12">
+        <v>3</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="12">
+        <v>3</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="12">
+        <v>2</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="12">
+        <v>2</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="12">
+        <v>11</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="12">
+        <v>12</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="12">
+        <v>8</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="12">
+        <v>15</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="12">
+        <v>40</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="12">
+        <v>3</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="12">
+        <v>3</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="12">
+        <v>3</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="12">
+        <v>26</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="12">
+        <v>14</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="12">
+        <v>20</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="12">
+        <v>10</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="12">
+        <v>40</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="12">
+        <v>1</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="12">
+        <v>1</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="12">
+        <v>2</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="12">
+        <v>250</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="12">
+        <v>100</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="12">
+        <v>3</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="12">
+        <v>50</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="12">
+        <v>8</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="12">
+        <v>64</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="12">
+        <v>128</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="12">
+        <v>100</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="12">
+        <v>100</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="12">
+        <v>20</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C65" s="11"/>
+      <c r="E65" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="67.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="67.6666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6666666666667" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2547,7 +4128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -2565,9 +4146,9 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>70</v>
@@ -2579,13 +4160,13 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -2605,7 +4186,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>53</v>
       </c>
@@ -2621,7 +4202,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -2641,7 +4222,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
         <v>69</v>
       </c>
@@ -2659,7 +4240,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
+    <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
         <v>71</v>
       </c>
@@ -2677,7 +4258,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
+    <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
         <v>74</v>
       </c>
@@ -2695,7 +4276,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:8">
+    <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
         <v>85</v>
       </c>
@@ -2707,7 +4288,7 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:8">
+    <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
         <v>86</v>
       </c>
@@ -2715,28 +4296,28 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:8">
+    <row r="14" spans="1:8">
       <c r="A14" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
+    <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>116</v>
+        <v>225</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C15" s="3"/>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:9">
+    <row r="17" spans="1:9">
       <c r="A17" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:9">
+    <row r="18" spans="1:9">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>41</v>
@@ -2745,14 +4326,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="1:9">
+    <row r="20" spans="1:9">
       <c r="A20" s="8" t="s">
         <v>92</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:9">
+    <row r="21" spans="1:9">
       <c r="A21" s="8" t="s">
         <v>93</v>
       </c>
@@ -2786,12 +4367,12 @@
         <v>102</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>118</v>
+        <v>227</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
       <c r="E22" s="11" t="s">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
@@ -2800,15 +4381,15 @@
     </row>
     <row r="23" customFormat="1" spans="1:9">
       <c r="A23" s="11" t="s">
-        <v>120</v>
+        <v>229</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>121</v>
+        <v>220</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="12"/>
-      <c r="E23" s="11" t="s">
-        <v>122</v>
+      <c r="E23" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
@@ -2818,40 +4399,40 @@
       <c r="I23" s="12"/>
     </row>
     <row r="24" customFormat="1" spans="1:9">
-      <c r="A24" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
+      <c r="A24" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
       <c r="E24" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+        <v>230</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
       <c r="H24" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I24" s="13"/>
+      <c r="I24" s="12"/>
     </row>
     <row r="25" customFormat="1" spans="1:9">
-      <c r="A25" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
+      <c r="A25" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
       <c r="E25" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
+        <v>230</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
     </row>
     <row r="26" customFormat="1"/>
     <row r="27" customFormat="1"/>
@@ -2870,37 +4451,37 @@
     <row r="38" customFormat="1"/>
     <row r="39" customFormat="1"/>
     <row r="40" customFormat="1"/>
-    <row r="50" s="1" customFormat="1" spans="5:5">
+    <row r="50" spans="5:5">
       <c r="E50" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="5:5">
-      <c r="E51" s="15" t="s">
+    <row r="51" spans="5:5">
+      <c r="E51" s="18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" spans="5:5">
+    <row r="52" spans="5:5">
       <c r="E52" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="5:5">
+    <row r="53" spans="5:5">
       <c r="E53" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" spans="5:5">
+    <row r="54" spans="5:5">
       <c r="E54" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="5:5">
+    <row r="55" spans="5:5">
       <c r="E55" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="5:5">
+    <row r="56" spans="5:5">
       <c r="E56" s="1" t="s">
         <v>112</v>
       </c>
